--- a/TemplateFinanciero_0.1.xlsx
+++ b/TemplateFinanciero_0.1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Santiago\Documents\Personal\Novus\tecbooks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B1831A0-0700-4D02-BAF5-813F856E0E55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D138B86-500D-4BED-B2C9-0498E6ADF54F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="651" activeTab="6" xr2:uid="{4E254C54-9BE2-42C1-A0A8-9417C5E2CF9F}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="651" activeTab="9" xr2:uid="{4E254C54-9BE2-42C1-A0A8-9417C5E2CF9F}"/>
   </bookViews>
   <sheets>
     <sheet name="Premisas" sheetId="5" r:id="rId1"/>
@@ -1451,8 +1451,8 @@
     <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
     <numFmt numFmtId="166" formatCode="#,##0.00_ ;[Red]\-#,##0.00\ "/>
-    <numFmt numFmtId="171" formatCode="0.000%"/>
-    <numFmt numFmtId="172" formatCode="#,##0.000000000000000_ ;[Red]\-#,##0.000000000000000\ "/>
+    <numFmt numFmtId="167" formatCode="0.000%"/>
+    <numFmt numFmtId="168" formatCode="#,##0.000000000000000_ ;[Red]\-#,##0.000000000000000\ "/>
   </numFmts>
   <fonts count="12" x14ac:knownFonts="1">
     <font>
@@ -1785,7 +1785,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="95">
+  <cellXfs count="91">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1889,24 +1889,20 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="44" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="44" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="44" fontId="0" fillId="4" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="44" fontId="0" fillId="10" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
     <xf numFmtId="43" fontId="0" fillId="5" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="43" fontId="0" fillId="5" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="171" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="44" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="44" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="44" fontId="0" fillId="4" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="172" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="44" fontId="0" fillId="10" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
-    <xf numFmtId="44" fontId="0" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Comma 2" xfId="5" xr:uid="{E6ADD19D-BFA4-4CC7-A73D-27D7C3DBF77B}"/>
@@ -13057,11 +13053,11 @@
         <v>163409695.94599998</v>
       </c>
       <c r="C10" s="59">
-        <f t="shared" ref="C10:L10" si="2">SUM(C3:C8)</f>
+        <f>SUM(C3:C8)</f>
         <v>647035302.06664813</v>
       </c>
       <c r="D10" s="59">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="D10:L10" si="2">SUM(D3:D8)</f>
         <v>1029557896.838227</v>
       </c>
       <c r="E10" s="59">
@@ -13107,11 +13103,11 @@
       <c r="A13" s="24" t="s">
         <v>363</v>
       </c>
-      <c r="B13" s="85">
+      <c r="B13" s="83">
         <f>'Estado R'!B9</f>
         <v>122420600</v>
       </c>
-      <c r="C13" s="85">
+      <c r="C13" s="83">
         <f>'Estado R'!C9</f>
         <v>126582900.40000001</v>
       </c>
@@ -13156,11 +13152,11 @@
       <c r="A14" s="24" t="s">
         <v>316</v>
       </c>
-      <c r="B14" s="85">
+      <c r="B14" s="83">
         <f>'Estado R'!B10</f>
         <v>5359707.6263999995</v>
       </c>
-      <c r="C14" s="85">
+      <c r="C14" s="83">
         <f>'Estado R'!C10</f>
         <v>5541937.6856975993</v>
       </c>
@@ -13205,11 +13201,11 @@
       <c r="A15" s="24" t="s">
         <v>364</v>
       </c>
-      <c r="B15" s="91">
+      <c r="B15" s="83">
         <f>'Estado R'!B11</f>
         <v>1742780.7478</v>
       </c>
-      <c r="C15" s="85">
+      <c r="C15" s="83">
         <f>'Estado R'!C11</f>
         <v>1802035.2932252001</v>
       </c>
@@ -13254,11 +13250,11 @@
       <c r="A16" s="24" t="s">
         <v>365</v>
       </c>
-      <c r="B16" s="91">
+      <c r="B16" s="83">
         <f>'Estado R'!B12</f>
         <v>2005511.5138000003</v>
       </c>
-      <c r="C16" s="85">
+      <c r="C16" s="83">
         <f>'Estado R'!C12</f>
         <v>2073698.9052692004</v>
       </c>
@@ -13303,11 +13299,11 @@
       <c r="A17" s="24" t="s">
         <v>366</v>
       </c>
-      <c r="B17" s="85">
+      <c r="B17" s="83">
         <f>'Estado R'!B13</f>
         <v>6080000</v>
       </c>
-      <c r="C17" s="85">
+      <c r="C17" s="83">
         <f>'Estado R'!C13</f>
         <v>33351442.520000007</v>
       </c>
@@ -13352,11 +13348,11 @@
       <c r="A18" s="24" t="s">
         <v>367</v>
       </c>
-      <c r="B18" s="85">
+      <c r="B18" s="83">
         <f>Egresos!B154</f>
         <v>7794346.0579999993</v>
       </c>
-      <c r="C18" s="85">
+      <c r="C18" s="83">
         <f>Egresos!C154</f>
         <v>8059353.8239719998</v>
       </c>
@@ -13401,11 +13397,11 @@
       <c r="A19" t="s">
         <v>368</v>
       </c>
-      <c r="B19" s="87">
+      <c r="B19" s="85">
         <f>Egresos!B206</f>
         <v>5316000</v>
       </c>
-      <c r="C19" s="87">
+      <c r="C19" s="85">
         <f>Egresos!C206</f>
         <v>5496744</v>
       </c>
@@ -13455,7 +13451,7 @@
       <c r="A21" t="s">
         <v>370</v>
       </c>
-      <c r="B21" s="87">
+      <c r="B21" s="85">
         <f>Egresos!B210</f>
         <v>8060000</v>
       </c>
@@ -13464,7 +13460,7 @@
       <c r="A22" t="s">
         <v>371</v>
       </c>
-      <c r="B22" s="87">
+      <c r="B22" s="85">
         <f>Egresos!B209</f>
         <v>6053000</v>
       </c>
@@ -13473,7 +13469,7 @@
       <c r="A23" t="s">
         <v>372</v>
       </c>
-      <c r="B23" s="87">
+      <c r="B23" s="85">
         <f>Egresos!B214</f>
         <v>2821000</v>
       </c>
@@ -13482,7 +13478,7 @@
       <c r="A24" t="s">
         <v>373</v>
       </c>
-      <c r="B24" s="87">
+      <c r="B24" s="85">
         <f>Egresos!B211</f>
         <v>217350</v>
       </c>
@@ -13491,7 +13487,7 @@
       <c r="A25" t="s">
         <v>374</v>
       </c>
-      <c r="B25" s="87">
+      <c r="B25" s="85">
         <f>Egresos!B212</f>
         <v>1440000</v>
       </c>
@@ -13500,23 +13496,23 @@
       <c r="A26" t="s">
         <v>375</v>
       </c>
-      <c r="B26" s="87">
+      <c r="B26" s="85">
         <f>'Estado R'!B33</f>
         <v>8161939.1891999999</v>
       </c>
-      <c r="C26" s="87">
+      <c r="C26" s="85">
         <f>'Estado R'!C33</f>
         <v>8161939.1891999999</v>
       </c>
-      <c r="D26" s="87">
+      <c r="D26" s="85">
         <f>'Estado R'!D33</f>
         <v>8161939.1891999999</v>
       </c>
-      <c r="E26" s="87">
+      <c r="E26" s="85">
         <f>'Estado R'!E33</f>
         <v>8161939.1891999999</v>
       </c>
-      <c r="F26" s="87">
+      <c r="F26" s="85">
         <f>'Estado R'!F33</f>
         <v>8161939.1891999999</v>
       </c>
@@ -13549,23 +13545,23 @@
       <c r="A27" t="s">
         <v>376</v>
       </c>
-      <c r="B27" s="87">
+      <c r="B27" s="85">
         <f>'Estado R'!B32</f>
         <v>5931009.1441519978</v>
       </c>
-      <c r="C27" s="87">
+      <c r="C27" s="85">
         <f>'Estado R'!C32</f>
         <v>4625098.8738799971</v>
       </c>
-      <c r="D27" s="87">
+      <c r="D27" s="85">
         <f>'Estado R'!D32</f>
         <v>3319188.6036079936</v>
       </c>
-      <c r="E27" s="87">
+      <c r="E27" s="85">
         <f>'Estado R'!E32</f>
         <v>2013278.3333359938</v>
       </c>
-      <c r="F27" s="90">
+      <c r="F27" s="87">
         <f>'Estado R'!F32</f>
         <v>897813.31081199087</v>
       </c>
@@ -13662,11 +13658,11 @@
         <v>183403244.27935198</v>
       </c>
       <c r="C32" s="56">
-        <f t="shared" ref="C32:L32" si="3">SUM(C13:C30)</f>
+        <f>SUM(C13:C30)</f>
         <v>355467466.17722112</v>
       </c>
       <c r="D32" s="56">
-        <f t="shared" si="3"/>
+        <f t="shared" ref="D32:L32" si="3">SUM(D13:D30)</f>
         <v>733920811.69744229</v>
       </c>
       <c r="E32" s="56">
@@ -13801,7 +13797,7 @@
         <f>IRR(B34:L34,3)</f>
         <v>14.59779326433766</v>
       </c>
-      <c r="C42" s="83"/>
+      <c r="C42" s="81"/>
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A43" s="1" t="s">
@@ -13839,7 +13835,8 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -26470,7 +26467,7 @@
       <c r="B122" s="24">
         <v>2</v>
       </c>
-      <c r="C122" s="85">
+      <c r="C122" s="83">
         <f>G14*B122*12</f>
         <v>350307.68800000002</v>
       </c>
@@ -26483,7 +26480,7 @@
       <c r="B123" s="24">
         <v>1</v>
       </c>
-      <c r="C123" s="85">
+      <c r="C123" s="83">
         <f>G28*B123*12</f>
         <v>289003.84259999997</v>
       </c>
@@ -26496,7 +26493,7 @@
       <c r="B124" s="24">
         <v>1</v>
       </c>
-      <c r="C124" s="85">
+      <c r="C124" s="83">
         <f>B124*K14*12</f>
         <v>262730.76599999995</v>
       </c>
@@ -26509,7 +26506,7 @@
       <c r="B125" s="24">
         <v>1</v>
       </c>
-      <c r="C125" s="85">
+      <c r="C125" s="83">
         <f>B125*O14*12</f>
         <v>262730.76599999995</v>
       </c>
@@ -26522,7 +26519,7 @@
       <c r="B126" s="24">
         <v>1</v>
       </c>
-      <c r="C126" s="85">
+      <c r="C126" s="83">
         <f>B126*K28*12</f>
         <v>289003.84259999997</v>
       </c>
@@ -26535,7 +26532,7 @@
       <c r="B127" s="24">
         <v>1</v>
       </c>
-      <c r="C127" s="85">
+      <c r="C127" s="83">
         <f>O28*B127*12</f>
         <v>289003.84259999997</v>
       </c>
@@ -26548,15 +26545,10 @@
       <c r="B128" s="77">
         <v>1</v>
       </c>
-      <c r="C128" s="84">
+      <c r="C128" s="82">
         <f>B128*O42*12</f>
         <v>367823.07240000006</v>
       </c>
-      <c r="D128" s="92"/>
-      <c r="E128" s="92"/>
-      <c r="F128" s="92"/>
-      <c r="G128" s="92"/>
-      <c r="H128" s="92"/>
     </row>
     <row r="129" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A129" s="77" t="str">
@@ -26566,15 +26558,10 @@
       <c r="B129" s="77">
         <v>1</v>
       </c>
-      <c r="C129" s="84">
+      <c r="C129" s="82">
         <f>C42*B129*12</f>
         <v>367823.07240000006</v>
       </c>
-      <c r="D129" s="92"/>
-      <c r="E129" s="92"/>
-      <c r="F129" s="92"/>
-      <c r="G129" s="92"/>
-      <c r="H129" s="92"/>
     </row>
     <row r="130" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A130" s="77" t="str">
@@ -26584,15 +26571,10 @@
       <c r="B130" s="77">
         <v>1</v>
       </c>
-      <c r="C130" s="84">
+      <c r="C130" s="82">
         <f>G42*B130*12</f>
         <v>367823.07240000006</v>
       </c>
-      <c r="D130" s="92"/>
-      <c r="E130" s="92"/>
-      <c r="F130" s="92"/>
-      <c r="G130" s="92"/>
-      <c r="H130" s="92"/>
     </row>
     <row r="131" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A131" s="77" t="str">
@@ -26602,15 +26584,10 @@
       <c r="B131" s="77">
         <v>1</v>
       </c>
-      <c r="C131" s="84">
+      <c r="C131" s="82">
         <f>K42*1*12</f>
         <v>289003.84259999997</v>
       </c>
-      <c r="D131" s="92"/>
-      <c r="E131" s="92"/>
-      <c r="F131" s="92"/>
-      <c r="G131" s="92"/>
-      <c r="H131" s="92"/>
     </row>
     <row r="132" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A132" s="77" t="str">
@@ -26620,15 +26597,10 @@
       <c r="B132" s="77">
         <v>1</v>
       </c>
-      <c r="C132" s="84">
+      <c r="C132" s="82">
         <f>C56*12</f>
         <v>613038.45400000003</v>
       </c>
-      <c r="D132" s="92"/>
-      <c r="E132" s="92"/>
-      <c r="F132" s="92"/>
-      <c r="G132" s="92"/>
-      <c r="H132" s="92"/>
     </row>
     <row r="133" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A133" t="str">
@@ -26642,11 +26614,6 @@
         <f>B133*C72*12</f>
         <v>735646.14480000013</v>
       </c>
-      <c r="D133" s="92"/>
-      <c r="E133" s="92"/>
-      <c r="F133" s="92"/>
-      <c r="G133" s="92"/>
-      <c r="H133" s="92"/>
     </row>
     <row r="134" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A134" t="str">
@@ -26660,11 +26627,6 @@
         <f>B134*G72*12</f>
         <v>875769.22000000009</v>
       </c>
-      <c r="D134" s="92"/>
-      <c r="E134" s="92"/>
-      <c r="F134" s="92"/>
-      <c r="G134" s="92"/>
-      <c r="H134" s="92"/>
     </row>
     <row r="135" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A135" t="str">
@@ -26678,11 +26640,6 @@
         <f>B135*K72*12</f>
         <v>1103469.2172000003</v>
       </c>
-      <c r="D135" s="92"/>
-      <c r="E135" s="92"/>
-      <c r="F135" s="92"/>
-      <c r="G135" s="92"/>
-      <c r="H135" s="92"/>
     </row>
     <row r="136" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A136" t="str">
@@ -26696,11 +26653,6 @@
         <f>B136*O72*12</f>
         <v>735646.14480000013</v>
       </c>
-      <c r="D136" s="92"/>
-      <c r="E136" s="92"/>
-      <c r="F136" s="92"/>
-      <c r="G136" s="92"/>
-      <c r="H136" s="92"/>
     </row>
     <row r="137" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A137" t="str">
@@ -26714,11 +26666,6 @@
         <f>B137*C86*12</f>
         <v>315276.9192</v>
       </c>
-      <c r="D137" s="92"/>
-      <c r="E137" s="92"/>
-      <c r="F137" s="92"/>
-      <c r="G137" s="92"/>
-      <c r="H137" s="92"/>
     </row>
     <row r="138" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A138" t="str">
@@ -26732,11 +26679,6 @@
         <f>G86*12</f>
         <v>437884.61000000004</v>
       </c>
-      <c r="D138" s="92"/>
-      <c r="E138" s="92"/>
-      <c r="F138" s="92"/>
-      <c r="G138" s="92"/>
-      <c r="H138" s="92"/>
     </row>
     <row r="139" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A139" t="str">
@@ -26750,11 +26692,6 @@
         <f>B139*K86*12</f>
         <v>437884.61000000004</v>
       </c>
-      <c r="D139" s="92"/>
-      <c r="E139" s="92"/>
-      <c r="F139" s="92"/>
-      <c r="G139" s="92"/>
-      <c r="H139" s="94"/>
     </row>
     <row r="140" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A140" t="str">
@@ -26768,11 +26705,6 @@
         <f>B140*O86*12</f>
         <v>613038.45400000003</v>
       </c>
-      <c r="D140" s="92"/>
-      <c r="E140" s="92"/>
-      <c r="F140" s="92"/>
-      <c r="G140" s="92"/>
-      <c r="H140" s="92"/>
     </row>
     <row r="141" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A141" t="str">
@@ -26786,11 +26718,6 @@
         <f>C100*B141*12</f>
         <v>875769.22000000009</v>
       </c>
-      <c r="D141" s="92"/>
-      <c r="E141" s="92"/>
-      <c r="F141" s="92"/>
-      <c r="G141" s="92"/>
-      <c r="H141" s="92"/>
     </row>
     <row r="142" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A142" t="str">
@@ -26804,11 +26731,7 @@
         <f>C114*B142*12</f>
         <v>875769.22000000009</v>
       </c>
-      <c r="D142" s="92"/>
-      <c r="E142" s="92"/>
-      <c r="F142" s="92"/>
-      <c r="G142" s="92"/>
-      <c r="H142" s="93"/>
+      <c r="H142" s="88"/>
     </row>
     <row r="143" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A143" t="str">
@@ -26822,11 +26745,7 @@
         <f>B143*G114*12</f>
         <v>525461.53200000001</v>
       </c>
-      <c r="D143" s="92"/>
-      <c r="E143" s="92"/>
-      <c r="F143" s="92"/>
-      <c r="G143" s="92"/>
-      <c r="H143" s="93"/>
+      <c r="H143" s="88"/>
     </row>
     <row r="144" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A144" t="str">
@@ -26840,11 +26759,7 @@
         <f>B144*K114*12</f>
         <v>262730.76599999995</v>
       </c>
-      <c r="D144" s="92"/>
-      <c r="E144" s="92"/>
-      <c r="F144" s="92"/>
-      <c r="G144" s="92"/>
-      <c r="H144" s="93"/>
+      <c r="H144" s="88"/>
     </row>
     <row r="145" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
@@ -26854,43 +26769,18 @@
         <f>SUM(C120:C144)</f>
         <v>16902345.945999999</v>
       </c>
-      <c r="D145" s="92"/>
-      <c r="E145" s="92"/>
-      <c r="F145" s="92"/>
-      <c r="G145" s="92"/>
-      <c r="H145" s="93"/>
-    </row>
-    <row r="146" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="D146" s="92"/>
-      <c r="E146" s="92"/>
-      <c r="F146" s="92"/>
-      <c r="G146" s="92"/>
-      <c r="H146" s="92"/>
+      <c r="H145" s="88"/>
     </row>
     <row r="147" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
         <v>227</v>
       </c>
-      <c r="D147" s="92"/>
-      <c r="E147" s="92"/>
-      <c r="F147" s="92"/>
-      <c r="G147" s="92"/>
-      <c r="H147" s="92"/>
     </row>
     <row r="148" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B148" s="39"/>
-      <c r="D148" s="92"/>
-      <c r="E148" s="92"/>
-      <c r="F148" s="92"/>
-      <c r="G148" s="92"/>
-      <c r="H148" s="92"/>
     </row>
     <row r="149" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="D149" s="88"/>
-      <c r="E149" s="92"/>
-      <c r="F149" s="92"/>
-      <c r="G149" s="92"/>
-      <c r="H149" s="92"/>
+      <c r="D149" s="39"/>
     </row>
     <row r="150" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B150" s="24">
@@ -27794,7 +27684,7 @@
         <f>SUM(B209:B214)</f>
         <v>40809695.945999995</v>
       </c>
-      <c r="D215" s="89"/>
+      <c r="D215" s="86"/>
     </row>
     <row r="218" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A218" t="s">
@@ -29023,7 +28913,7 @@
         <f>Egresos!B178</f>
         <v>122420600</v>
       </c>
-      <c r="C9" s="86">
+      <c r="C9" s="84">
         <v>126582900.40000001</v>
       </c>
       <c r="D9" s="39">
@@ -30038,14 +29928,14 @@
       <c r="D52" t="s">
         <v>453</v>
       </c>
-      <c r="E52" s="81">
+      <c r="E52" s="89">
         <f>B54/(E50-B60)</f>
         <v>26066.884178522654</v>
       </c>
       <c r="G52" t="s">
         <v>456</v>
       </c>
-      <c r="H52" s="81">
+      <c r="H52" s="89">
         <f>B54/((E50-B60)/E50)</f>
         <v>198108319.75677216</v>
       </c>
@@ -30061,11 +29951,11 @@
       <c r="D53" t="s">
         <v>454</v>
       </c>
-      <c r="E53" s="82"/>
+      <c r="E53" s="90"/>
       <c r="G53" t="s">
         <v>454</v>
       </c>
-      <c r="H53" s="82"/>
+      <c r="H53" s="90"/>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A54" s="1" t="s">
@@ -30102,14 +29992,14 @@
       <c r="D58" t="s">
         <v>457</v>
       </c>
-      <c r="E58" s="81">
+      <c r="E58" s="89">
         <f>(B54+E56)/(E50-B60)</f>
         <v>26479.771338514009</v>
       </c>
       <c r="G58" t="s">
         <v>456</v>
       </c>
-      <c r="H58" s="81">
+      <c r="H58" s="89">
         <f>(B54+E56)/((E50-B60)/E50)</f>
         <v>201246262.17270645</v>
       </c>
@@ -30125,11 +30015,11 @@
       <c r="D59" t="s">
         <v>458</v>
       </c>
-      <c r="E59" s="82"/>
+      <c r="E59" s="90"/>
       <c r="G59" t="s">
         <v>454</v>
       </c>
-      <c r="H59" s="82"/>
+      <c r="H59" s="90"/>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A60" s="1" t="s">
